--- a/data/trans_orig/IP05A07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A07-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36660</t>
+          <t>36464</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52262</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30745</t>
+          <t>31428</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45880</t>
+          <t>46301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71657</t>
+          <t>71836</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92987</t>
+          <t>94536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28050</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44102</t>
+          <t>43946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31336</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47187</t>
+          <t>46340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64670</t>
+          <t>62736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86080</t>
+          <t>86004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28080</t>
+          <t>28684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238273</t>
+          <t>238928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>273268</t>
+          <t>272742</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>256443</t>
+          <t>255435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>292865</t>
+          <t>292842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>504886</t>
+          <t>504518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>555991</t>
+          <t>553830</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134339</t>
+          <t>134913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>166375</t>
+          <t>167046</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>141841</t>
+          <t>141581</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>176702</t>
+          <t>176868</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>284992</t>
+          <t>288653</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>332341</t>
+          <t>336620</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35771</t>
+          <t>35609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56644</t>
+          <t>56554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49792</t>
+          <t>48836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73476</t>
+          <t>75176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91440</t>
+          <t>91561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123959</t>
+          <t>124930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70770</t>
+          <t>71722</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91844</t>
+          <t>93113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73017</t>
+          <t>72740</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94600</t>
+          <t>93716</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>149128</t>
+          <t>150812</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>179587</t>
+          <t>180825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47103</t>
+          <t>46994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66966</t>
+          <t>67623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51814</t>
+          <t>51991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73268</t>
+          <t>73598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105680</t>
+          <t>104557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135017</t>
+          <t>133254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37623</t>
+          <t>37370</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>34792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44120</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67109</t>
+          <t>66636</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>358991</t>
+          <t>359659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>402388</t>
+          <t>402182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>376320</t>
+          <t>374084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>420573</t>
+          <t>419322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>747850</t>
+          <t>745626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>809765</t>
+          <t>809467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>223365</t>
+          <t>223314</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264601</t>
+          <t>263770</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>237731</t>
+          <t>241022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>281646</t>
+          <t>283034</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>474524</t>
+          <t>475668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>534496</t>
+          <t>533676</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72452</t>
+          <t>73045</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101619</t>
+          <t>102445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80459</t>
+          <t>81962</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111039</t>
+          <t>111720</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>160955</t>
+          <t>162474</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>202244</t>
+          <t>204034</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29527</t>
+          <t>29496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41877</t>
+          <t>41663</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36643</t>
+          <t>36327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49516</t>
+          <t>49065</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69546</t>
+          <t>69410</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87491</t>
+          <t>88577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11328</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23026</t>
+          <t>22907</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42448</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>296097</t>
+          <t>297192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>329058</t>
+          <t>328763</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306438</t>
+          <t>304975</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>340121</t>
+          <t>340358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>611431</t>
+          <t>612493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>658027</t>
+          <t>659076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104375</t>
+          <t>105935</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>135500</t>
+          <t>135509</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100766</t>
+          <t>101773</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131701</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>215129</t>
+          <t>214460</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>258429</t>
+          <t>255989</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28432</t>
+          <t>28222</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>47259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37566</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>60666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72362</t>
+          <t>72726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101330</t>
+          <t>99459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99798</t>
+          <t>99687</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119669</t>
+          <t>120779</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117244</t>
+          <t>116322</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138782</t>
+          <t>137227</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>223083</t>
+          <t>221995</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>252638</t>
+          <t>250978</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32919</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50425</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31521</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49900</t>
+          <t>50877</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68697</t>
+          <t>70460</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94055</t>
+          <t>94393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>29344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30991</t>
+          <t>31369</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51360</t>
+          <t>51769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>439118</t>
+          <t>437997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>478984</t>
+          <t>479318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>472449</t>
+          <t>470904</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>515004</t>
+          <t>513778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>924459</t>
+          <t>924272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>983019</t>
+          <t>981435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160046</t>
+          <t>158543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196175</t>
+          <t>197663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154001</t>
+          <t>156565</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192618</t>
+          <t>193426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>325908</t>
+          <t>324861</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379028</t>
+          <t>378203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>52900</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79214</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>63987</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>91419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124306</t>
+          <t>124477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162039</t>
+          <t>159978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>39031</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50070</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40942</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53174</t>
+          <t>53543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83901</t>
+          <t>85487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100797</t>
+          <t>101534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11336</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>18379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266145</t>
+          <t>268652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362022</t>
+          <t>362999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>384818</t>
+          <t>385765</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>422312</t>
+          <t>421223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>672903</t>
+          <t>665854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>771581</t>
+          <t>771016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64320</t>
+          <t>64031</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173002</t>
+          <t>168542</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57599</t>
+          <t>58114</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90189</t>
+          <t>87774</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>132089</t>
+          <t>131795</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>237363</t>
+          <t>239778</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23412</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43510</t>
+          <t>43027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30312</t>
+          <t>31696</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54229</t>
+          <t>54312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61291</t>
+          <t>59718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90267</t>
+          <t>89687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96790</t>
+          <t>96685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>115066</t>
+          <t>115139</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>116825</t>
+          <t>118554</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>141325</t>
+          <t>141395</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>221414</t>
+          <t>222969</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>250703</t>
+          <t>250982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32514</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43591</t>
+          <t>43772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45161</t>
+          <t>43778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70205</t>
+          <t>68646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28839</t>
+          <t>28912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30134</t>
+          <t>29299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50107</t>
+          <t>50298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>423296</t>
+          <t>410265</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>517636</t>
+          <t>517139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>558493</t>
+          <t>558039</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>605025</t>
+          <t>605183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1005769</t>
+          <t>999638</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1107058</t>
+          <t>1106032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94219</t>
+          <t>91954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194047</t>
+          <t>204289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>91371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130986</t>
+          <t>130487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>195725</t>
+          <t>198797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>303754</t>
+          <t>307113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42850</t>
+          <t>43018</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66454</t>
+          <t>66814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56054</t>
+          <t>54324</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85387</t>
+          <t>85544</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>105277</t>
+          <t>106374</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143872</t>
+          <t>143721</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP05A07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A07-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38773</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31498</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46707</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>43613</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36464</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52224</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35981</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>52033</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>47,61%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38773</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31428</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>46301</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>44,98%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71836</t>
+          <t>71534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94536</t>
+          <t>93889</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38767</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31385</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>46553</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>35899</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28566</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>43946</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28899</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>44262</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,19%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38767</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>31680</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>46340</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62736</t>
+          <t>64274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86004</t>
+          <t>86314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8652</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4673</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14719</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>12090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7394</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18639</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7605</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>18596</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,2%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8652</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4830</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14617</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>29292</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>274162</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>257423</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>291940</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>55,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>52,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>255761</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>238928</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>272742</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>237454</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>273276</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>56,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>274162</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>255435</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>292842</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>55,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>504518</t>
+          <t>503207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>553830</t>
+          <t>550412</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,18%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>159282</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>142819</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>177358</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>32,21%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>28,88%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>35,87%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149912</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>134913</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>167046</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>134304</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>166354</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>33,2%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>36,99%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>159282</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>141581</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>176868</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>32,21%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>288653</t>
+          <t>287386</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>336620</t>
+          <t>335552</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>61002</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73366</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>45910</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35609</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56554</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>36456</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>58089</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>61002</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>48836</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>75176</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91561</t>
+          <t>92422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124930</t>
+          <t>123517</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>451583</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>451583</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>451583</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>83692</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73714</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>95102</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>48,59%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>55,22%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>81676</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>71722</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>93113</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>71153</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>92722</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>48,96%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>43,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>55,82%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>83692</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>72740</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>93716</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>48,59%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>150812</t>
+          <t>149071</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>180825</t>
+          <t>179145</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>52,84%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62262</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>51865</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>72782</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>56847</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>46994</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>67623</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>46683</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>67772</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>34,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>62262</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>51991</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>73598</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>36,15%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104557</t>
+          <t>105173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133254</t>
+          <t>133861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26274</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19204</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>28289</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20606</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37370</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20147</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37499</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>16,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>26274</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>19037</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>34792</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43996</t>
+          <t>44266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66636</t>
+          <t>66824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>396627</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>373743</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>420172</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>553</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>381050</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>359659</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>402182</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>360552</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>404369</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,67%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>50,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>396627</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>374084</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>419322</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,68%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>745626</t>
+          <t>746388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>809467</t>
+          <t>810040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>260311</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>236683</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>282728</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>242657</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>223314</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>263770</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>219620</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>262769</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,18%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>260311</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>241022</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>283034</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>475668</t>
+          <t>473423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>533676</t>
+          <t>530766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>95928</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>82044</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>111189</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,9%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14,77%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>86289</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>73045</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>102445</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>73036</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>100948</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>12,15%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>10,29%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>95928</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>81962</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>111720</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>162474</t>
+          <t>162600</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>204034</t>
+          <t>204001</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>709996</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>709996</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>709996</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2609,7 +2609,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2777,72 +2777,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43122</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35822</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49132</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>62,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>36203</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29496</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41663</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>30071</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>41989</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>60,97%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>43122</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36327</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>49065</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>62,85%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69410</t>
+          <t>69876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88577</t>
+          <t>87355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -2890,72 +2890,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16815</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11259</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23227</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16790</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11910</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22701</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11807</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22444</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16815</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11429</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22907</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26112</t>
+          <t>26038</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42672</t>
+          <t>42165</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -3003,72 +3003,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8677</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13861</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,2%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6385</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3072</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11107</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3172</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11600</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,75%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,71%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8677</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4831</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14180</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>22197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -3116,57 +3116,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3233,72 +3233,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>322919</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>305695</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>340367</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>62,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>313187</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>297192</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>328763</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>297345</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>331181</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,56%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,87%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>322919</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>304975</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>340358</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,16%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>612493</t>
+          <t>612288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>659076</t>
+          <t>660645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -3346,72 +3346,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>116166</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101009</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>132117</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23,8%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20,7%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>27,07%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>119958</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>105935</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>135509</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>104389</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>135075</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>25,49%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>116166</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101773</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>131994</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>214460</t>
+          <t>216000</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>255989</t>
+          <t>257124</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -3459,72 +3459,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48972</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39045</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60986</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>37406</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28222</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47259</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>28546</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>47508</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,95%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>48972</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>60666</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72726</t>
+          <t>72681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99459</t>
+          <t>100624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -3572,57 +3572,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>488057</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>488057</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>488057</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>470552</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>470552</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>470552</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>488057</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>488057</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>488057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3689,72 +3689,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>127446</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>117248</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>138592</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>67,97%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>62,53%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>73,92%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>109749</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>99687</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>120779</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>99663</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>119764</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>63,75%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>57,9%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>70,16%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>127446</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116322</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>137227</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>67,97%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>221995</t>
+          <t>222049</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>250978</t>
+          <t>251345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -3802,72 +3802,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>40460</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30962</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49295</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>41231</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32316</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50445</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32866</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50674</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,95%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>40460</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>32030</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>50877</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,58%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70460</t>
+          <t>69257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94393</t>
+          <t>94761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -3915,72 +3915,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19589</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13353</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27909</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>21179</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14640</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29344</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>28525</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>12,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>19589</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>13660</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>27681</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31369</t>
+          <t>32026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51769</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -4028,57 +4028,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172159</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172159</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172159</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4145,72 +4145,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>493486</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>471451</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>514241</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>63,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>69,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>693</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>459140</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>437997</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>479318</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>439424</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>479630</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>65,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>493486</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>470904</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>513778</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>66,31%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>924272</t>
+          <t>922504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>981435</t>
+          <t>982155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -4258,72 +4258,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>173441</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>156287</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>193765</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,31%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>177979</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>158543</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>197663</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>160443</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>197385</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>25,35%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>173441</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>156565</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>193426</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>23,31%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324861</t>
+          <t>324986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378203</t>
+          <t>377358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -4371,72 +4371,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>77239</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>63623</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>90263</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>64969</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>52900</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>77780</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>53358</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>77694</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>9,25%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>77239</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>63987</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>91419</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124477</t>
+          <t>124675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>159978</t>
+          <t>162827</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -4484,57 +4484,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>702089</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>702089</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>702089</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4664,7 +4664,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4832,72 +4832,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43880</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37685</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48947</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>77,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>66,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>45620</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39031</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49917</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>83,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>47793</t>
+          <t>36487</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41036</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53543</t>
+          <t>40426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4907,32 +4907,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>93413</t>
+          <t>80367</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85487</t>
+          <t>71893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101534</t>
+          <t>86839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -4945,72 +4945,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5543</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10084</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6423</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3139</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11857</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>12139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5020,32 +5020,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>23,27%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2635</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7384</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>914</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5133,32 +5133,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -5171,57 +5171,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5288,72 +5288,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>367907</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>349606</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>383368</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>77,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>73,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>501</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>336358</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>268652</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>362999</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>403235</t>
+          <t>330720</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>385765</t>
+          <t>314126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>421223</t>
+          <t>344300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5363,32 +5363,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>739593</t>
+          <t>698627</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>665854</t>
+          <t>673291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>771016</t>
+          <t>721340</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -5401,72 +5401,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>69123</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>54508</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>84623</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>17,79%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>91519</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>64031</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>168542</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>13,9%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>36,6%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71790</t>
+          <t>68899</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58114</t>
+          <t>55812</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87774</t>
+          <t>83932</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5476,32 +5476,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>163309</t>
+          <t>138022</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>131795</t>
+          <t>118492</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>239778</t>
+          <t>162057</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -5514,72 +5514,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38648</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28330</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>49882</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>32632</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24230</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43027</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41594</t>
+          <t>32828</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31696</t>
+          <t>25105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54312</t>
+          <t>42939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5589,32 +5589,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>74226</t>
+          <t>71476</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59718</t>
+          <t>58562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89687</t>
+          <t>87495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -5627,57 +5627,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5702,17 +5702,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5744,72 +5744,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>120936</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>110184</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>130277</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>72,22%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>65,8%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>77,8%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>106787</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>96685</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>115139</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>71,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>64,65%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>76,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>130710</t>
+          <t>107041</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118554</t>
+          <t>97426</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>141395</t>
+          <t>115436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5819,32 +5819,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>237498</t>
+          <t>227977</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>222969</t>
+          <t>213764</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>250982</t>
+          <t>240533</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -5857,72 +5857,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28209</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21007</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>37755</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>23670</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17019</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>31801</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31614</t>
+          <t>23679</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23555</t>
+          <t>16873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43772</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5932,32 +5932,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>55284</t>
+          <t>51888</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43778</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68646</t>
+          <t>64053</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -5970,72 +5970,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18317</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11710</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>26372</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>19093</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12733</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27421</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6045,32 +6045,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>37573</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29299</t>
+          <t>28705</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50298</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -6083,57 +6083,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6158,17 +6158,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6200,72 +6200,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>532723</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>511552</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>554024</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>76,12%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>488765</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>410265</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>517139</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>73,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>581738</t>
+          <t>474248</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>558039</t>
+          <t>454972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>605183</t>
+          <t>492195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6275,32 +6275,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1070503</t>
+          <t>1006971</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>999638</t>
+          <t>976782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1106032</t>
+          <t>1034906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -6313,72 +6313,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>102875</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>85200</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121560</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,7%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>121613</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>91954</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>204289</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>109682</t>
+          <t>99667</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91371</t>
+          <t>85042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130487</t>
+          <t>117071</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6388,32 +6388,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>231295</t>
+          <t>202542</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>198797</t>
+          <t>177443</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307113</t>
+          <t>227125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -6426,72 +6426,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>64274</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51615</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>79534</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>54360</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>43018</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>66814</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69608</t>
+          <t>55267</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54324</t>
+          <t>43313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85544</t>
+          <t>67242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6501,32 +6501,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>123969</t>
+          <t>119541</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>103289</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143721</t>
+          <t>141051</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -6539,57 +6539,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
